--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104763_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104763_W34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.582100000000001</v>
+        <v>9.421900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5866</v>
+        <v>7.8932</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9954</v>
+        <v>1.5287</v>
       </c>
       <c r="G2" t="n">
         <v>7.1343</v>
@@ -610,13 +610,13 @@
         <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5507</v>
+        <v>0.2892</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0283</v>
+        <v>0.2783</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5224</v>
+        <v>0.0108</v>
       </c>
       <c r="V2" t="n">
         <v>0.8603</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5788</v>
+        <v>5.6727</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7858</v>
+        <v>4.6591</v>
       </c>
       <c r="F3" t="n">
-        <v>1.793</v>
+        <v>1.0136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6595</v>
+        <v>3.6553</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7635999999999999</v>
+        <v>2.7025</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.104</v>
+        <v>0.9528</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0023</v>
+        <v>4.1416</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7789</v>
+        <v>2.8613</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2234</v>
+        <v>1.2803</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3428</v>
+        <v>-0.4863</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0154</v>
+        <v>-0.1588</v>
       </c>
       <c r="O3" t="n">
         <v>-0.3275</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4553</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5934</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0558</v>
+        <v>0.1963</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0402</v>
+        <v>0.3597</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0157</v>
+        <v>-0.1634</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4082</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8814</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4733</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8749</v>
+        <v>4.6415</v>
       </c>
       <c r="E4" t="n">
-        <v>3.83</v>
+        <v>3.3817</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0449</v>
+        <v>1.2598</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6553</v>
+        <v>0.6595</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7025</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9528</v>
+        <v>-0.104</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1416</v>
+        <v>1.0023</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8613</v>
+        <v>0.7789</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2803</v>
+        <v>0.2234</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4863</v>
+        <v>-0.3428</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1588</v>
+        <v>-0.0154</v>
       </c>
       <c r="O4" t="n">
         <v>-0.3275</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8211</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8211</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6014</v>
+        <v>1.1185</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4694</v>
+        <v>0.6361</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.132</v>
+        <v>0.4824</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.4082</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1578</v>
+        <v>2.8814</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1578</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7772</v>
+        <v>2.5273</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4643</v>
+        <v>2.3914</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3129</v>
+        <v>0.1359</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5667</v>
+        <v>4.5968</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9044</v>
+        <v>1.8989</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3378</v>
+        <v>2.6979</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3148</v>
+        <v>6.0291</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0542</v>
+        <v>2.5748</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2607</v>
+        <v>3.4543</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7481</v>
+        <v>-1.4323</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1497</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5984</v>
+        <v>-0.7563</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9105</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1382</v>
+        <v>-4.5526</v>
       </c>
       <c r="R5" t="n">
         <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0025</v>
+        <v>-0.1103</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7428</v>
+        <v>-0.1745</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2596</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7025</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5447</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2472</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.765</v>
+        <v>2.2668</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1526</v>
+        <v>1.7485</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5183</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4487</v>
@@ -922,13 +922,13 @@
         <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.461</v>
+        <v>0.9628</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0402</v>
+        <v>0.6361</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4208</v>
+        <v>0.3267</v>
       </c>
       <c r="V6" t="n">
         <v>0.387</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3948</v>
+        <v>2.258</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7295</v>
+        <v>2.6351</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3346</v>
+        <v>-0.3771</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5968</v>
+        <v>1.5667</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8989</v>
+        <v>1.9044</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6979</v>
+        <v>-0.3378</v>
       </c>
       <c r="J7" t="n">
-        <v>6.0291</v>
+        <v>3.3148</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5748</v>
+        <v>3.0542</v>
       </c>
       <c r="L7" t="n">
-        <v>3.4543</v>
+        <v>0.2607</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4323</v>
+        <v>-1.7481</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.1497</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7563</v>
+        <v>-0.5984</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.5039</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5526</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
         <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2427</v>
+        <v>0.4833</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8364</v>
+        <v>-0.0863</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4063</v>
+        <v>0.5696</v>
       </c>
       <c r="V7" t="n">
+        <v>-0.7025</v>
+      </c>
+      <c r="W7" t="n">
         <v>0.5447</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.0895</v>
-      </c>
       <c r="X7" t="n">
-        <v>-0.5447</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HANDS</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2588</v>
+        <v>0.0312</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9537</v>
+        <v>0.291</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6949</v>
+        <v>-0.2598</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1872</v>
+        <v>0.2331</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.1823</v>
+        <v>0.3242</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9951</v>
+        <v>-0.0911</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6548</v>
+        <v>1.6802</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.2483</v>
+        <v>0.9136</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5935</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5325</v>
+        <v>-1.4471</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.5893</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5984</v>
+        <v>-0.8578</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1382</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2671</v>
+        <v>-0.4994</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0229</v>
+        <v>-0.251</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2442</v>
+        <v>-0.2483</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1789</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7237</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5447</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>J. HANDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3938</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0541</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.448</v>
+        <v>-0.6635</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2331</v>
+        <v>-2.1872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3242</v>
+        <v>-3.1823</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0911</v>
+        <v>0.9951</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6802</v>
+        <v>-0.6548</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9136</v>
+        <v>-2.2483</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7665999999999999</v>
+        <v>1.5935</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4471</v>
+        <v>-1.5325</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5893</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8578</v>
+        <v>-0.5984</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4553</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5934</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9245</v>
+        <v>-0.0569</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4879</v>
+        <v>-0.3324</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4365</v>
+        <v>0.2755</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1578</v>
+        <v>2.1789</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1578</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.989</v>
+        <v>-1.069</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8556</v>
+        <v>-1.0924</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1334</v>
+        <v>0.0234</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0596</v>
@@ -1234,13 +1234,13 @@
         <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1601</v>
+        <v>0.0801</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4596</v>
+        <v>0.2228</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2995</v>
+        <v>-0.1427</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3133</v>
+        <v>-1.1879</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7594</v>
+        <v>-1.5713</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4462</v>
+        <v>0.3834</v>
       </c>
       <c r="G11" t="n">
         <v>0.1907</v>
@@ -1312,13 +1312,13 @@
         <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.325</v>
+        <v>-0.1996</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.697</v>
+        <v>-0.5089</v>
       </c>
       <c r="U11" t="n">
-        <v>0.372</v>
+        <v>0.3093</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6342</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5881</v>
+        <v>-2.2014</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3788</v>
+        <v>-0.0235</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2093</v>
+        <v>-2.1779</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7286</v>
@@ -1390,13 +1390,13 @@
         <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9081</v>
+        <v>-0.5214</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9061</v>
+        <v>-0.5508</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.002</v>
+        <v>0.0294</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6342</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.9474</v>
+        <v>22.2959</v>
       </c>
       <c r="E13" t="n">
-        <v>20.5628</v>
+        <v>20.9111</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3846</v>
+        <v>1.3848</v>
       </c>
       <c r="G13" t="n">
         <v>12.6123</v>
@@ -1453,13 +1453,13 @@
         <v>-10.3827</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.753100000000001</v>
+        <v>-5.7531</v>
       </c>
       <c r="O13" t="n">
         <v>-4.6294</v>
       </c>
       <c r="P13" t="n">
-        <v>5.691000000000001</v>
+        <v>5.691</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.52</v>
@@ -1468,13 +1468,13 @@
         <v>18.2106</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3941</v>
+        <v>1.742599999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1194</v>
+        <v>0.2291000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5136</v>
+        <v>1.5135</v>
       </c>
       <c r="V13" t="n">
         <v>2.2504</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6543</v>
+        <v>2.6159</v>
       </c>
       <c r="E14" t="n">
-        <v>3.476</v>
+        <v>3.5945</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8217</v>
+        <v>-0.9786</v>
       </c>
       <c r="G14" t="n">
         <v>2.4289</v>
@@ -1546,13 +1546,13 @@
         <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6807</v>
+        <v>0.6423</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0229</v>
+        <v>0.1414</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5569</v>
+        <v>1.2097</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8355</v>
+        <v>1.3618</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2786</v>
+        <v>-0.1521</v>
       </c>
       <c r="G15" t="n">
         <v>-2.2842</v>
@@ -1624,13 +1624,13 @@
         <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5923</v>
+        <v>0.2451</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0217</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4294</v>
+        <v>-0.3028</v>
       </c>
       <c r="V15" t="n">
         <v>2.5659</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1806</v>
+        <v>0.7514</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8403</v>
+        <v>3.6534</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0209</v>
+        <v>-2.902</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2442</v>
+        <v>-1.302</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.74</v>
+        <v>1.2122</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4958</v>
+        <v>-2.5141</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9327</v>
+        <v>1.362</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0072</v>
+        <v>2.0027</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0745</v>
+        <v>-0.6407</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6886</v>
+        <v>-2.664</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7328</v>
+        <v>-0.7906</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4214</v>
+        <v>-1.8734</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4553</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2276</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6829</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1882</v>
+        <v>-0.4019</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1623</v>
+        <v>-0.4324</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3505</v>
+        <v>0.0305</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1578</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1578</v>
+        <v>2.7237</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.1038</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1796</v>
+        <v>-1.3141</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0902</v>
+        <v>1.2102</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.302</v>
+        <v>-0.2442</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2122</v>
+        <v>-1.74</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5141</v>
+        <v>1.4958</v>
       </c>
       <c r="J17" t="n">
-        <v>1.362</v>
+        <v>-0.9327</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0027</v>
+        <v>-1.0072</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6407</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.664</v>
+        <v>0.6886</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7906</v>
+        <v>-0.7328</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8734</v>
+        <v>1.4214</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3658</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6829</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.4727</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.3115</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.1612</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.3658</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-1.0639</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.9061</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.1577</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.0895</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.7237</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>D. GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4646</v>
+        <v>-0.1545</v>
       </c>
       <c r="E18" t="n">
-        <v>0.038</v>
+        <v>-0.0984</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5026</v>
+        <v>-0.0562</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8477</v>
+        <v>1.1357</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9876</v>
+        <v>0.7813</v>
       </c>
       <c r="I18" t="n">
-        <v>0.14</v>
+        <v>0.3544</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5610000000000001</v>
+        <v>2.1526</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4417</v>
+        <v>1.1549</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1194</v>
+        <v>0.9977</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2866</v>
+        <v>-1.0169</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.546</v>
+        <v>-0.3736</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2593</v>
+        <v>-0.6433</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6829</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6829</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7896</v>
+        <v>0.2334</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5991</v>
+        <v>0.0253</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1906</v>
+        <v>0.208</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0895</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0895</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. GARCIA</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4785</v>
+        <v>-0.5103</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4537</v>
+        <v>0.593</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0248</v>
+        <v>-1.1034</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1357</v>
+        <v>-0.6686</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7813</v>
+        <v>-1.3645</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3544</v>
+        <v>0.6959</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1526</v>
+        <v>2.1241</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1549</v>
+        <v>-0.028</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9977</v>
+        <v>2.1521</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0169</v>
+        <v>-2.7927</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3736</v>
+        <v>-1.3365</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6433</v>
+        <v>-1.4562</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3658</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2763</v>
+        <v>-3.6421</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9105</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0906</v>
+        <v>-0.4272</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.33</v>
+        <v>-0.2257</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2394</v>
+        <v>-0.2016</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1578</v>
+        <v>2.1789</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X19" t="n">
         <v>-0.1578</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6959</v>
+        <v>-0.8199</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0008</v>
+        <v>-0.3173</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6967</v>
+        <v>-0.5026</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6686</v>
+        <v>-0.8477</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3645</v>
+        <v>-0.9876</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6959</v>
+        <v>0.14</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1241</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.028</v>
+        <v>-0.4417</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1521</v>
+        <v>-0.1194</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7927</v>
+        <v>-0.2866</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3365</v>
+        <v>-0.546</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4562</v>
+        <v>0.2593</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5934</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6421</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0487</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6128</v>
+        <v>0.4343</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8179</v>
+        <v>0.2437</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2051</v>
+        <v>0.1906</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1789</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3367</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1578</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3276</v>
+        <v>-2.0382</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1948</v>
+        <v>0.4842</v>
       </c>
       <c r="F21" t="n">
         <v>-2.5224</v>
@@ -2092,10 +2092,10 @@
         <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5793</v>
+        <v>0.8686</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3887</v>
+        <v>0.678</v>
       </c>
       <c r="U21" t="n">
         <v>0.1906</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0231</v>
+        <v>-3.9463</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8062</v>
+        <v>-1.0431</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2169</v>
+        <v>-2.9032</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8498</v>
@@ -2170,13 +2170,13 @@
         <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7667</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2559</v>
+        <v>-0.4928</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5108</v>
+        <v>-0.1972</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0895</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8409</v>
+        <v>-4.2346</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.144</v>
+        <v>-0.7887</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6968</v>
+        <v>-3.4459</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6072</v>
@@ -2248,13 +2248,13 @@
         <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0547</v>
+        <v>-0.4484</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1664</v>
+        <v>-0.8111</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1117</v>
+        <v>0.3627</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6342</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2729</v>
+        <v>-6.2404</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7324</v>
+        <v>-4.1401</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5405</v>
+        <v>-2.1003</v>
       </c>
       <c r="G24" t="n">
         <v>-2.331</v>
@@ -2326,13 +2326,13 @@
         <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2102</v>
+        <v>-0.1778</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7667</v>
+        <v>-0.1745</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4435</v>
+        <v>-0.0033</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5447</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.3253</v>
+        <v>-7.6866</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1328</v>
+        <v>-3.3697</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.1925</v>
+        <v>-4.3169</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1855</v>
@@ -2404,13 +2404,13 @@
         <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0488</v>
+        <v>-0.4101</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.465</v>
+        <v>-0.7019</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4162</v>
+        <v>0.2919</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4976</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.9476</v>
+        <v>-21.1576</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.384700000000001</v>
+        <v>-1.384500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-20.5628</v>
+        <v>-19.7734</v>
       </c>
       <c r="G26" t="n">
         <v>-12.6122</v>
@@ -2473,7 +2473,7 @@
         <v>-9.200699999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.6907</v>
+        <v>-5.690700000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.2105</v>
@@ -2482,13 +2482,13 @@
         <v>12.5198</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.394</v>
+        <v>-0.6043999999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.5133</v>
+        <v>-1.5136</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1195000000000001</v>
+        <v>0.9092</v>
       </c>
       <c r="V26" t="n">
         <v>-2.2504</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104763_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104763_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.9567</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104763_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-10.2072</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
